--- a/data/trans_orig/P21D_6_R-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/P21D_6_R-Provincia-trans_orig.xlsx
@@ -535,7 +535,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que, necesitando atención fisioterapéutica, no la pudo recibir por motivos económicos en 2023</t>
+          <t>Población que, necesitando atención fisioterapéutica, no la pudo recibir por motivos económicos en 2023 (tasa de respuesta: 99,77%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -730,97 +730,97 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>1005</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>1921</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>3591</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>0,8%</t>
+        </is>
+      </c>
+      <c r="O4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>1,25%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>2,84%</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="K4" s="2" t="inlineStr">
+      <c r="R4" s="2" t="inlineStr">
         <is>
           <t>1005</t>
         </is>
       </c>
-      <c r="L4" s="2" t="inlineStr">
+      <c r="S4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>3072</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>0,8%</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
+      <c r="T4" s="2" t="inlineStr">
+        <is>
+          <t>3338</t>
+        </is>
+      </c>
+      <c r="U4" s="2" t="inlineStr">
+        <is>
+          <t>0,36%</t>
+        </is>
+      </c>
+      <c r="V4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>2,43%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>1005</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>3493</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>0,36%</t>
-        </is>
-      </c>
-      <c r="V4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>1,24%</t>
+          <t>1,19%</t>
         </is>
       </c>
     </row>
@@ -843,12 +843,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>152345</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>154266</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -858,12 +858,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>98,75%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -878,7 +878,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>123245</t>
+          <t>122726</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -893,7 +893,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>97,57%</t>
+          <t>97,16%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -913,7 +913,7 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>277090</t>
+          <t>277245</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
@@ -928,7 +928,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>98,76%</t>
+          <t>98,81%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -1073,12 +1073,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1663</t>
+          <t>1392</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>12770</t>
+          <t>13035</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1088,12 +1088,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>0,66%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>6,07%</t>
+          <t>6,2%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1108,12 +1108,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>592</t>
+          <t>660</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>5572</t>
+          <t>5436</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1123,12 +1123,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,25%</t>
+          <t>0,28%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>2,36%</t>
+          <t>2,3%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1143,12 +1143,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>2700</t>
+          <t>2956</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>15290</t>
+          <t>14529</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1158,12 +1158,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,66%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>3,43%</t>
+          <t>3,25%</t>
         </is>
       </c>
     </row>
@@ -1186,12 +1186,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>197474</t>
+          <t>197209</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>208581</t>
+          <t>208852</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1201,12 +1201,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>93,93%</t>
+          <t>93,8%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,21%</t>
+          <t>99,34%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1221,12 +1221,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>230561</t>
+          <t>230697</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>235541</t>
+          <t>235473</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1236,12 +1236,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>97,64%</t>
+          <t>97,7%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>99,75%</t>
+          <t>99,72%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1256,12 +1256,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>431087</t>
+          <t>431848</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>443677</t>
+          <t>443421</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1271,12 +1271,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>96,57%</t>
+          <t>96,75%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,4%</t>
+          <t>99,34%</t>
         </is>
       </c>
     </row>
@@ -1421,7 +1421,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>6279</t>
+          <t>7086</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1436,7 +1436,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>6,62%</t>
+          <t>7,47%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1451,12 +1451,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>5354</t>
+          <t>5302</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>13998</t>
+          <t>14234</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>3,68%</t>
+          <t>3,64%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>9,62%</t>
+          <t>9,78%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1486,12 +1486,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>6809</t>
+          <t>6206</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>17503</t>
+          <t>17467</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,83%</t>
+          <t>2,58%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>7,28%</t>
+          <t>7,26%</t>
         </is>
       </c>
     </row>
@@ -1529,7 +1529,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>88633</t>
+          <t>87826</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>93,38%</t>
+          <t>92,53%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1564,12 +1564,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>131543</t>
+          <t>131307</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>140187</t>
+          <t>140239</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1579,12 +1579,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>90,38%</t>
+          <t>90,22%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>96,32%</t>
+          <t>96,36%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1599,12 +1599,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>222950</t>
+          <t>222986</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>233644</t>
+          <t>234247</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1614,12 +1614,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>92,72%</t>
+          <t>92,74%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>97,17%</t>
+          <t>97,42%</t>
         </is>
       </c>
     </row>
@@ -1764,7 +1764,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>6648</t>
+          <t>6235</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1779,7 +1779,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>4,7%</t>
+          <t>4,41%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1799,7 +1799,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>4017</t>
+          <t>4027</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1829,12 +1829,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>612</t>
+          <t>559</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>7595</t>
+          <t>7351</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1844,12 +1844,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,16%</t>
+          <t>0,14%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>1,96%</t>
+          <t>1,9%</t>
         </is>
       </c>
     </row>
@@ -1872,7 +1872,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>134729</t>
+          <t>135142</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1887,7 +1887,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>95,3%</t>
+          <t>95,59%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1907,7 +1907,7 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>242543</t>
+          <t>242533</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>380342</t>
+          <t>380586</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>387325</t>
+          <t>387378</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1957,12 +1957,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>98,04%</t>
+          <t>98,1%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,84%</t>
+          <t>99,86%</t>
         </is>
       </c>
     </row>
@@ -2102,97 +2102,97 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>1243</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>1,76%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
+      <c r="O16" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P16" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q16" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K16" s="2" t="inlineStr">
+      <c r="R16" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>835</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
+      <c r="S16" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T16" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U16" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O16" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P16" s="2" t="inlineStr">
-        <is>
-          <t>1,17%</t>
-        </is>
-      </c>
-      <c r="Q16" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R16" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S16" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T16" s="2" t="inlineStr">
-        <is>
-          <t>1002</t>
-        </is>
-      </c>
-      <c r="U16" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>0,71%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -2215,12 +2215,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>69461</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>70704</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2230,12 +2230,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>98,24%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2250,12 +2250,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>70527</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>71362</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2265,12 +2265,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>98,83%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2285,12 +2285,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>141064</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>142066</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2300,12 +2300,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>99,29%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -2445,97 +2445,97 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K19" s="2" t="inlineStr">
+        <is>
+          <t>515</t>
+        </is>
+      </c>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>1354</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>2745</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
+        <is>
+          <t>0,46%</t>
+        </is>
+      </c>
+      <c r="O19" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>1,08%</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
+      <c r="P19" s="2" t="inlineStr">
+        <is>
+          <t>2,47%</t>
+        </is>
+      </c>
+      <c r="Q19" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K19" s="2" t="inlineStr">
+      <c r="R19" s="2" t="inlineStr">
         <is>
           <t>515</t>
         </is>
       </c>
-      <c r="L19" s="2" t="inlineStr">
+      <c r="S19" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t>3065</t>
-        </is>
-      </c>
-      <c r="N19" s="2" t="inlineStr">
-        <is>
-          <t>0,46%</t>
-        </is>
-      </c>
-      <c r="O19" s="2" t="inlineStr">
+      <c r="T19" s="2" t="inlineStr">
+        <is>
+          <t>2136</t>
+        </is>
+      </c>
+      <c r="U19" s="2" t="inlineStr">
+        <is>
+          <t>0,22%</t>
+        </is>
+      </c>
+      <c r="V19" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P19" s="2" t="inlineStr">
-        <is>
-          <t>2,76%</t>
-        </is>
-      </c>
-      <c r="Q19" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R19" s="2" t="inlineStr">
-        <is>
-          <t>515</t>
-        </is>
-      </c>
-      <c r="S19" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T19" s="2" t="inlineStr">
-        <is>
-          <t>3401</t>
-        </is>
-      </c>
-      <c r="U19" s="2" t="inlineStr">
-        <is>
-          <t>0,22%</t>
-        </is>
-      </c>
-      <c r="V19" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>1,44%</t>
+          <t>0,9%</t>
         </is>
       </c>
     </row>
@@ -2558,12 +2558,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>124240</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>125594</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2573,12 +2573,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>98,92%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2593,7 +2593,7 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>107887</t>
+          <t>108207</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
@@ -2608,7 +2608,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>97,24%</t>
+          <t>97,53%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2628,7 +2628,7 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>233145</t>
+          <t>234410</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
@@ -2643,7 +2643,7 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>98,56%</t>
+          <t>99,1%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
@@ -2788,12 +2788,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>2094</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2803,12 +2803,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>0,67%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2823,12 +2823,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>2420</t>
+          <t>2092</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>12445</t>
+          <t>11614</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2838,12 +2838,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>0,68%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>4,06%</t>
+          <t>3,79%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2858,12 +2858,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>2373</t>
+          <t>2145</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>12461</t>
+          <t>12201</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2873,12 +2873,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0,38%</t>
+          <t>0,35%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>2,02%</t>
+          <t>1,97%</t>
         </is>
       </c>
     </row>
@@ -2901,12 +2901,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>308862</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>310956</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2916,12 +2916,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>99,33%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2936,12 +2936,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>294409</t>
+          <t>295240</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>304434</t>
+          <t>304762</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2951,12 +2951,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>95,94%</t>
+          <t>96,21%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>99,21%</t>
+          <t>99,32%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2971,12 +2971,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>605349</t>
+          <t>605609</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>615437</t>
+          <t>615665</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2986,12 +2986,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>97,98%</t>
+          <t>98,03%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>99,62%</t>
+          <t>99,65%</t>
         </is>
       </c>
     </row>
@@ -3131,82 +3131,82 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K25" s="2" t="inlineStr">
+        <is>
+          <t>550</t>
+        </is>
+      </c>
+      <c r="L25" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F25" s="2" t="inlineStr">
-        <is>
-          <t>3183</t>
-        </is>
-      </c>
-      <c r="G25" s="2" t="inlineStr">
+      <c r="M25" s="2" t="inlineStr">
+        <is>
+          <t>2429</t>
+        </is>
+      </c>
+      <c r="N25" s="2" t="inlineStr">
+        <is>
+          <t>0,16%</t>
+        </is>
+      </c>
+      <c r="O25" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H25" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I25" s="2" t="inlineStr">
-        <is>
-          <t>0,57%</t>
-        </is>
-      </c>
-      <c r="J25" s="2" t="inlineStr">
+      <c r="P25" s="2" t="inlineStr">
+        <is>
+          <t>0,7%</t>
+        </is>
+      </c>
+      <c r="Q25" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K25" s="2" t="inlineStr">
+      <c r="R25" s="2" t="inlineStr">
         <is>
           <t>550</t>
         </is>
       </c>
-      <c r="L25" s="2" t="inlineStr">
+      <c r="S25" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M25" s="2" t="inlineStr">
-        <is>
-          <t>2762</t>
-        </is>
-      </c>
-      <c r="N25" s="2" t="inlineStr">
-        <is>
-          <t>0,16%</t>
-        </is>
-      </c>
-      <c r="O25" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="P25" s="2" t="inlineStr">
-        <is>
-          <t>0,79%</t>
-        </is>
-      </c>
-      <c r="Q25" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R25" s="2" t="inlineStr">
-        <is>
-          <t>550</t>
-        </is>
-      </c>
-      <c r="S25" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>3072</t>
+          <t>3078</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3244,12 +3244,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>550733</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>553916</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3259,12 +3259,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>99,43%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3279,7 +3279,7 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>346187</t>
+          <t>346520</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
@@ -3294,7 +3294,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>99,21%</t>
+          <t>99,3%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3314,7 +3314,7 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>899792</t>
+          <t>899786</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
@@ -3474,12 +3474,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>3352</t>
+          <t>3735</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>17969</t>
+          <t>17563</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>0,22%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>1,06%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3509,12 +3509,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>13392</t>
+          <t>13469</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>29039</t>
+          <t>29134</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3524,12 +3524,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>0,85%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>1,82%</t>
+          <t>1,83%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3544,12 +3544,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>19536</t>
+          <t>19316</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>40407</t>
+          <t>39603</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3559,12 +3559,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,59%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>1,24%</t>
+          <t>1,22%</t>
         </is>
       </c>
     </row>
@@ -3587,12 +3587,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>1644000</t>
+          <t>1644406</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>1658617</t>
+          <t>1658234</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3602,12 +3602,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>98,92%</t>
+          <t>98,94%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>99,8%</t>
+          <t>99,78%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3622,12 +3622,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>1563628</t>
+          <t>1563533</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>1579275</t>
+          <t>1579198</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3637,12 +3637,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>98,18%</t>
+          <t>98,17%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>99,16%</t>
+          <t>99,15%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3657,12 +3657,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>3214229</t>
+          <t>3215033</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>3235100</t>
+          <t>3235320</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3672,12 +3672,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>98,76%</t>
+          <t>98,78%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>99,4%</t>
+          <t>99,41%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P21D_6_R-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/P21D_6_R-Provincia-trans_orig.xlsx
@@ -760,7 +760,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>1005</t>
+          <t>985</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
@@ -770,12 +770,12 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>3591</t>
+          <t>2986</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,71%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
@@ -785,7 +785,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>2,84%</t>
+          <t>2,15%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,7 +795,7 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>1005</t>
+          <t>985</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
@@ -805,12 +805,12 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>3338</t>
+          <t>3110</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>0,36%</t>
+          <t>0,34%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
@@ -820,7 +820,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,06%</t>
         </is>
       </c>
     </row>
@@ -838,7 +838,7 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>154266</t>
+          <t>154287</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -873,27 +873,27 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>125312</t>
+          <t>137724</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>122726</t>
+          <t>135723</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>126317</t>
+          <t>138709</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>99,2%</t>
+          <t>99,29%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>97,16%</t>
+          <t>97,85%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -908,27 +908,27 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>279578</t>
+          <t>292011</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>277245</t>
+          <t>289886</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>280583</t>
+          <t>292996</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>99,64%</t>
+          <t>99,66%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>98,81%</t>
+          <t>98,94%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -951,17 +951,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>154266</t>
+          <t>154287</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>154266</t>
+          <t>154287</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>154266</t>
+          <t>154287</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -986,17 +986,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>126317</t>
+          <t>138709</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>126317</t>
+          <t>138709</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>126317</t>
+          <t>138709</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1021,17 +1021,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>280583</t>
+          <t>292996</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>280583</t>
+          <t>292996</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>280583</t>
+          <t>292996</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1068,32 +1068,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>4945</t>
+          <t>5056</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1392</t>
+          <t>1313</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>13035</t>
+          <t>12732</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>2,35%</t>
+          <t>2,29%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>0,59%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>6,2%</t>
+          <t>5,77%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1103,32 +1103,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>2017</t>
+          <t>2509</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>660</t>
+          <t>611</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>5436</t>
+          <t>6237</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>0,85%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,28%</t>
+          <t>0,24%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>2,48%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1138,32 +1138,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>6962</t>
+          <t>7565</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>2956</t>
+          <t>3229</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>14529</t>
+          <t>15608</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>1,56%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>0,68%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>3,25%</t>
+          <t>3,3%</t>
         </is>
       </c>
     </row>
@@ -1181,32 +1181,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>205299</t>
+          <t>215673</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>197209</t>
+          <t>207997</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>208852</t>
+          <t>219416</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>97,65%</t>
+          <t>97,71%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>93,8%</t>
+          <t>94,23%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,34%</t>
+          <t>99,41%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1216,32 +1216,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>234116</t>
+          <t>249019</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>230697</t>
+          <t>245291</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>235473</t>
+          <t>250917</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>99,15%</t>
+          <t>99,0%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>97,7%</t>
+          <t>97,52%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>99,72%</t>
+          <t>99,76%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1251,32 +1251,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>439415</t>
+          <t>464692</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>431848</t>
+          <t>456649</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>443421</t>
+          <t>469028</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>98,44%</t>
+          <t>98,4%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>96,75%</t>
+          <t>96,7%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,34%</t>
+          <t>99,32%</t>
         </is>
       </c>
     </row>
@@ -1294,17 +1294,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>210244</t>
+          <t>220729</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>210244</t>
+          <t>220729</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>210244</t>
+          <t>220729</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1329,17 +1329,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>236133</t>
+          <t>251528</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>236133</t>
+          <t>251528</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>236133</t>
+          <t>251528</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1364,17 +1364,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>446377</t>
+          <t>472257</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>446377</t>
+          <t>472257</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>446377</t>
+          <t>472257</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1411,7 +1411,7 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>1968</t>
+          <t>1845</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -1421,12 +1421,12 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>7086</t>
+          <t>6886</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>2,07%</t>
+          <t>1,98%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
@@ -1436,7 +1436,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>7,47%</t>
+          <t>7,4%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1446,32 +1446,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>9114</t>
+          <t>9237</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>5302</t>
+          <t>5496</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>14234</t>
+          <t>14648</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>6,26%</t>
+          <t>6,31%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>3,64%</t>
+          <t>3,76%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>9,78%</t>
+          <t>10,01%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1481,32 +1481,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>11082</t>
+          <t>11081</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>6206</t>
+          <t>6957</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>17467</t>
+          <t>17325</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>4,61%</t>
+          <t>4,63%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,58%</t>
+          <t>2,91%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>7,26%</t>
+          <t>7,24%</t>
         </is>
       </c>
     </row>
@@ -1524,27 +1524,27 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>92944</t>
+          <t>91209</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>87826</t>
+          <t>86168</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>94912</t>
+          <t>93054</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>97,93%</t>
+          <t>98,02%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>92,53%</t>
+          <t>92,6%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1559,32 +1559,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>136427</t>
+          <t>137105</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>131307</t>
+          <t>131694</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>140239</t>
+          <t>140846</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>93,74%</t>
+          <t>93,69%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>90,22%</t>
+          <t>89,99%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>96,36%</t>
+          <t>96,24%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1594,32 +1594,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>229371</t>
+          <t>228315</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>222986</t>
+          <t>222071</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>234247</t>
+          <t>232439</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>95,39%</t>
+          <t>95,37%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>92,74%</t>
+          <t>92,76%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>97,42%</t>
+          <t>97,09%</t>
         </is>
       </c>
     </row>
@@ -1637,17 +1637,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>94912</t>
+          <t>93054</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>94912</t>
+          <t>93054</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>94912</t>
+          <t>93054</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1672,17 +1672,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>145541</t>
+          <t>146342</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>145541</t>
+          <t>146342</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>145541</t>
+          <t>146342</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1707,17 +1707,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>240453</t>
+          <t>239396</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>240453</t>
+          <t>239396</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>240453</t>
+          <t>239396</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1754,7 +1754,7 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>1684</t>
+          <t>1731</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -1764,12 +1764,12 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>6235</t>
+          <t>6638</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>0,99%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
@@ -1779,7 +1779,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>4,41%</t>
+          <t>3,8%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1789,7 +1789,7 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>1108</t>
+          <t>1184</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
@@ -1799,12 +1799,12 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>4027</t>
+          <t>4062</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>0,45%</t>
+          <t>0,59%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
@@ -1814,7 +1814,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>1,63%</t>
+          <t>2,02%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1824,32 +1824,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>2792</t>
+          <t>2915</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>559</t>
+          <t>671</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>7351</t>
+          <t>7800</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>0,78%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,14%</t>
+          <t>0,18%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>2,07%</t>
         </is>
       </c>
     </row>
@@ -1867,27 +1867,27 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>139693</t>
+          <t>172729</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>135142</t>
+          <t>167822</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>141377</t>
+          <t>174460</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>98,81%</t>
+          <t>99,01%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>95,59%</t>
+          <t>96,2%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1902,27 +1902,27 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>245452</t>
+          <t>200324</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>242533</t>
+          <t>197446</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>246560</t>
+          <t>201508</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>99,55%</t>
+          <t>99,41%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>98,37%</t>
+          <t>97,98%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -1937,32 +1937,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>385145</t>
+          <t>373053</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>380586</t>
+          <t>368168</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>387378</t>
+          <t>375297</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>99,28%</t>
+          <t>99,22%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>98,1%</t>
+          <t>97,93%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,86%</t>
+          <t>99,82%</t>
         </is>
       </c>
     </row>
@@ -1980,17 +1980,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>141377</t>
+          <t>174460</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>141377</t>
+          <t>174460</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>141377</t>
+          <t>174460</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2015,17 +2015,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>246560</t>
+          <t>201508</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>246560</t>
+          <t>201508</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>246560</t>
+          <t>201508</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2050,17 +2050,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>387937</t>
+          <t>375968</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>387937</t>
+          <t>375968</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>387937</t>
+          <t>375968</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2210,7 +2210,7 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>70704</t>
+          <t>84421</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
@@ -2245,7 +2245,7 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>71362</t>
+          <t>79385</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
@@ -2280,7 +2280,7 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>142066</t>
+          <t>163806</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
@@ -2323,17 +2323,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>70704</t>
+          <t>84421</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>70704</t>
+          <t>84421</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>70704</t>
+          <t>84421</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2358,17 +2358,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>71362</t>
+          <t>79385</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>71362</t>
+          <t>79385</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>71362</t>
+          <t>79385</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2393,17 +2393,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>142066</t>
+          <t>163806</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>142066</t>
+          <t>163806</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>142066</t>
+          <t>163806</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2475,7 +2475,7 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>515</t>
+          <t>510</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
@@ -2485,12 +2485,12 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>2745</t>
+          <t>2143</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>0,46%</t>
+          <t>0,45%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
@@ -2500,7 +2500,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>2,47%</t>
+          <t>1,88%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2510,7 +2510,7 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>515</t>
+          <t>510</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
@@ -2520,12 +2520,12 @@
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>2136</t>
+          <t>3025</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>0,22%</t>
+          <t>0,21%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
@@ -2535,7 +2535,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>1,26%</t>
         </is>
       </c>
     </row>
@@ -2553,7 +2553,7 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>125594</t>
+          <t>126846</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
@@ -2588,27 +2588,27 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>110437</t>
+          <t>113206</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>108207</t>
+          <t>111573</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>110952</t>
+          <t>113716</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>99,54%</t>
+          <t>99,55%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>97,53%</t>
+          <t>98,12%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2623,27 +2623,27 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>236031</t>
+          <t>240052</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>234410</t>
+          <t>237537</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>236546</t>
+          <t>240562</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>99,78%</t>
+          <t>99,79%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>99,1%</t>
+          <t>98,74%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
@@ -2666,17 +2666,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>125594</t>
+          <t>126846</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>125594</t>
+          <t>126846</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>125594</t>
+          <t>126846</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2701,17 +2701,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>110952</t>
+          <t>113716</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>110952</t>
+          <t>113716</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>110952</t>
+          <t>113716</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2736,17 +2736,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>236546</t>
+          <t>240562</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>236546</t>
+          <t>240562</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>236546</t>
+          <t>240562</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2818,67 +2818,67 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>5612</t>
+          <t>5890</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>2092</t>
+          <t>2489</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>11614</t>
+          <t>12522</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
+          <t>1,65%</t>
+        </is>
+      </c>
+      <c r="O22" s="2" t="inlineStr">
+        <is>
+          <t>0,7%</t>
+        </is>
+      </c>
+      <c r="P22" s="2" t="inlineStr">
+        <is>
+          <t>3,52%</t>
+        </is>
+      </c>
+      <c r="Q22" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="R22" s="2" t="inlineStr">
+        <is>
+          <t>5890</t>
+        </is>
+      </c>
+      <c r="S22" s="2" t="inlineStr">
+        <is>
+          <t>2235</t>
+        </is>
+      </c>
+      <c r="T22" s="2" t="inlineStr">
+        <is>
+          <t>12991</t>
+        </is>
+      </c>
+      <c r="U22" s="2" t="inlineStr">
+        <is>
+          <t>0,83%</t>
+        </is>
+      </c>
+      <c r="V22" s="2" t="inlineStr">
+        <is>
+          <t>0,32%</t>
+        </is>
+      </c>
+      <c r="W22" s="2" t="inlineStr">
+        <is>
           <t>1,83%</t>
-        </is>
-      </c>
-      <c r="O22" s="2" t="inlineStr">
-        <is>
-          <t>0,68%</t>
-        </is>
-      </c>
-      <c r="P22" s="2" t="inlineStr">
-        <is>
-          <t>3,79%</t>
-        </is>
-      </c>
-      <c r="Q22" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="R22" s="2" t="inlineStr">
-        <is>
-          <t>5612</t>
-        </is>
-      </c>
-      <c r="S22" s="2" t="inlineStr">
-        <is>
-          <t>2145</t>
-        </is>
-      </c>
-      <c r="T22" s="2" t="inlineStr">
-        <is>
-          <t>12201</t>
-        </is>
-      </c>
-      <c r="U22" s="2" t="inlineStr">
-        <is>
-          <t>0,91%</t>
-        </is>
-      </c>
-      <c r="V22" s="2" t="inlineStr">
-        <is>
-          <t>0,35%</t>
-        </is>
-      </c>
-      <c r="W22" s="2" t="inlineStr">
-        <is>
-          <t>1,97%</t>
         </is>
       </c>
     </row>
@@ -2896,7 +2896,7 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>310956</t>
+          <t>351804</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
@@ -2931,67 +2931,67 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>301242</t>
+          <t>350289</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>295240</t>
+          <t>343657</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>304762</t>
+          <t>353690</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
+          <t>98,35%</t>
+        </is>
+      </c>
+      <c r="O23" s="2" t="inlineStr">
+        <is>
+          <t>96,48%</t>
+        </is>
+      </c>
+      <c r="P23" s="2" t="inlineStr">
+        <is>
+          <t>99,3%</t>
+        </is>
+      </c>
+      <c r="Q23" s="2" t="inlineStr">
+        <is>
+          <t>713</t>
+        </is>
+      </c>
+      <c r="R23" s="2" t="inlineStr">
+        <is>
+          <t>702093</t>
+        </is>
+      </c>
+      <c r="S23" s="2" t="inlineStr">
+        <is>
+          <t>694992</t>
+        </is>
+      </c>
+      <c r="T23" s="2" t="inlineStr">
+        <is>
+          <t>705748</t>
+        </is>
+      </c>
+      <c r="U23" s="2" t="inlineStr">
+        <is>
+          <t>99,17%</t>
+        </is>
+      </c>
+      <c r="V23" s="2" t="inlineStr">
+        <is>
           <t>98,17%</t>
         </is>
       </c>
-      <c r="O23" s="2" t="inlineStr">
-        <is>
-          <t>96,21%</t>
-        </is>
-      </c>
-      <c r="P23" s="2" t="inlineStr">
-        <is>
-          <t>99,32%</t>
-        </is>
-      </c>
-      <c r="Q23" s="2" t="inlineStr">
-        <is>
-          <t>713</t>
-        </is>
-      </c>
-      <c r="R23" s="2" t="inlineStr">
-        <is>
-          <t>612198</t>
-        </is>
-      </c>
-      <c r="S23" s="2" t="inlineStr">
-        <is>
-          <t>605609</t>
-        </is>
-      </c>
-      <c r="T23" s="2" t="inlineStr">
-        <is>
-          <t>615665</t>
-        </is>
-      </c>
-      <c r="U23" s="2" t="inlineStr">
-        <is>
-          <t>99,09%</t>
-        </is>
-      </c>
-      <c r="V23" s="2" t="inlineStr">
-        <is>
-          <t>98,03%</t>
-        </is>
-      </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>99,65%</t>
+          <t>99,68%</t>
         </is>
       </c>
     </row>
@@ -3009,17 +3009,17 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>310956</t>
+          <t>351804</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>310956</t>
+          <t>351804</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>310956</t>
+          <t>351804</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3044,17 +3044,17 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>306854</t>
+          <t>356179</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>306854</t>
+          <t>356179</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>306854</t>
+          <t>356179</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3079,17 +3079,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>617810</t>
+          <t>707983</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>617810</t>
+          <t>707983</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>617810</t>
+          <t>707983</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3161,7 +3161,7 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>550</t>
+          <t>615</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
@@ -3171,12 +3171,12 @@
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>2429</t>
+          <t>3518</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>0,16%</t>
+          <t>0,15%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
@@ -3186,7 +3186,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,86%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3196,7 +3196,7 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>550</t>
+          <t>615</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
@@ -3206,12 +3206,12 @@
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>3078</t>
+          <t>3718</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>0,06%</t>
+          <t>0,08%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
@@ -3221,7 +3221,7 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>0,34%</t>
+          <t>0,48%</t>
         </is>
       </c>
     </row>
@@ -3239,7 +3239,7 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>553916</t>
+          <t>360667</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
@@ -3274,27 +3274,27 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>348399</t>
+          <t>407114</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>346520</t>
+          <t>404211</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>348949</t>
+          <t>407729</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>99,84%</t>
+          <t>99,85%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>99,3%</t>
+          <t>99,14%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3309,27 +3309,27 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>902314</t>
+          <t>767781</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>899786</t>
+          <t>764678</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>902864</t>
+          <t>768396</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>99,94%</t>
+          <t>99,92%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>99,66%</t>
+          <t>99,52%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
@@ -3352,17 +3352,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>553916</t>
+          <t>360667</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>553916</t>
+          <t>360667</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>553916</t>
+          <t>360667</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3387,17 +3387,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>348949</t>
+          <t>407729</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>348949</t>
+          <t>407729</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>348949</t>
+          <t>407729</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3422,17 +3422,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>902864</t>
+          <t>768396</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>902864</t>
+          <t>768396</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>902864</t>
+          <t>768396</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3469,32 +3469,32 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>8597</t>
+          <t>8631</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>3735</t>
+          <t>3935</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>17563</t>
+          <t>17198</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>0,52%</t>
+          <t>0,55%</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>0,22%</t>
+          <t>0,25%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3504,32 +3504,32 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>19921</t>
+          <t>20929</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>13469</t>
+          <t>14057</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>29134</t>
+          <t>29193</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>1,23%</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>0,85%</t>
+          <t>0,83%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>1,83%</t>
+          <t>1,72%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3539,32 +3539,32 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>28518</t>
+          <t>29560</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>19316</t>
+          <t>21586</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>39603</t>
+          <t>40987</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>0,91%</t>
         </is>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>0,66%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>1,26%</t>
         </is>
       </c>
     </row>
@@ -3582,32 +3582,32 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>1653372</t>
+          <t>1557637</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>1644406</t>
+          <t>1549070</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>1658234</t>
+          <t>1562333</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>99,48%</t>
+          <t>99,45%</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>98,94%</t>
+          <t>98,9%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>99,78%</t>
+          <t>99,75%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3617,32 +3617,32 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>1572746</t>
+          <t>1674169</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>1563533</t>
+          <t>1665905</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>1579198</t>
+          <t>1681041</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>98,75%</t>
+          <t>98,77%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>98,17%</t>
+          <t>98,28%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>99,15%</t>
+          <t>99,17%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3652,32 +3652,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>3226118</t>
+          <t>3231805</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>3215033</t>
+          <t>3220378</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>3235320</t>
+          <t>3239779</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>99,12%</t>
+          <t>99,09%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>98,78%</t>
+          <t>98,74%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>99,41%</t>
+          <t>99,34%</t>
         </is>
       </c>
     </row>
@@ -3695,17 +3695,17 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>1661969</t>
+          <t>1566268</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>1661969</t>
+          <t>1566268</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>1661969</t>
+          <t>1566268</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3730,17 +3730,17 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>1592667</t>
+          <t>1695098</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>1592667</t>
+          <t>1695098</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>1592667</t>
+          <t>1695098</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3765,17 +3765,17 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>3254636</t>
+          <t>3261365</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>3254636</t>
+          <t>3261365</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>3254636</t>
+          <t>3261365</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
